--- a/templates/oefen/oefen_opdracht_template.xlsx
+++ b/templates/oefen/oefen_opdracht_template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6402" uniqueCount="1754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6399" uniqueCount="1754">
   <si>
     <t>naam</t>
   </si>
@@ -5249,25 +5249,25 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-02-10 16:32:33.599942</t>
+    <t>2026-03-31 16:51:56.427718</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.2.3</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>9.4.3</t>
+    <t>10.1.0</t>
   </si>
   <si>
     <t>schema-version</t>
   </si>
   <si>
-    <t>5.9.0</t>
+    <t>5.10.0</t>
   </si>
   <si>
     <t>mode</t>
@@ -26004,7 +26004,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="3" customWidth="1"/>
@@ -26064,10 +26064,9 @@
     <col min="57" max="57" width="34.7109375" style="3" customWidth="1"/>
     <col min="58" max="58" width="48.7109375" style="3" customWidth="1"/>
     <col min="59" max="59" width="40.7109375" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" hidden="1">
+    <row r="1" spans="1:59" hidden="1">
       <c r="A1" s="6" t="s">
         <v>174</v>
       </c>
@@ -26245,11 +26244,8 @@
       <c r="BG1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" hidden="1">
+    </row>
+    <row r="2" spans="1:59" hidden="1">
       <c r="A2" s="7" t="s">
         <v>175</v>
       </c>
@@ -26337,11 +26333,8 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" hidden="1">
+    </row>
+    <row r="3" spans="1:59" hidden="1">
       <c r="A3" s="7" t="s">
         <v>175</v>
       </c>
@@ -26456,7 +26449,7 @@
       </c>
       <c r="BG3" s="1"/>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:59" hidden="1">
       <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
@@ -26539,7 +26532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:60" hidden="1">
+    <row r="5" spans="1:59" hidden="1">
       <c r="K5" s="7" t="s">
         <v>192</v>
       </c>
@@ -26592,7 +26585,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:59">
       <c r="A6" s="6" t="s">
         <v>174</v>
       </c>
@@ -26769,9 +26762,6 @@
       </c>
       <c r="BG6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/templates/oefen/oefen_opdracht_template.xlsx
+++ b/templates/oefen/oefen_opdracht_template.xlsx
@@ -5255,19 +5255,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:38.145221</t>
+    <t>2026-05-19 11:29:12.162291</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>

--- a/templates/oefen/oefen_opdracht_template.xlsx
+++ b/templates/oefen/oefen_opdracht_template.xlsx
@@ -5255,13 +5255,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:29:12.162291</t>
+    <t>2026-05-19 14:53:02.896996</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
